--- a/XLibur.Tests/Resource/Other/PivotTable/TableProps/Property_layout_sets_layout_of_pivot_table_and_all_fields-outline.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTable/TableProps/Property_layout_sets_layout_of_pivot_table_and_all_fields-outline.xlsx
@@ -132,32 +132,36 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pivot table" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" compact="0" outline="1" outlineData="1" compactData="0">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="6">
-    <pivotField name="Name" axis="axisRow" compact="0" showAll="0" defaultSubtotal="0">
-      <items count="2">
+    <pivotField name="Name" axis="axisRow" compact="0" showAll="0">
+      <items count="3">
         <item x="0"/>
         <item x="1"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField name="Size" axis="axisRow" compact="0" showAll="0" defaultSubtotal="0">
-      <items count="2">
+    <pivotField name="Size" axis="axisRow" compact="0" showAll="0">
+      <items count="3">
         <item x="0"/>
         <item x="1"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField name="Month" axis="axisCol" compact="0" showAll="0" defaultSubtotal="0">
-      <items count="2">
+    <pivotField name="Month" axis="axisCol" compact="0" showAll="0">
+      <items count="3">
         <item x="0"/>
         <item x="1"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField name="Season" axis="axisCol" compact="0" showAll="0" defaultSubtotal="0">
-      <items count="2">
+    <pivotField name="Season" axis="axisCol" compact="0" showAll="0">
+      <items count="3">
         <item x="0"/>
         <item x="1"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="0"/>

--- a/XLibur.Tests/Resource/Other/PivotTable/TableProps/Property_layout_sets_layout_of_pivot_table_and_all_fields-outline.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTable/TableProps/Property_layout_sets_layout_of_pivot_table_and_all_fields-outline.xlsx
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pivot table" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" compact="0" outline="1" outlineData="1" compactData="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pivot table" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" compact="0" outline="1" outlineData="1" compactData="0">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="6">
     <pivotField name="Name" axis="axisRow" compact="0" showAll="0">
